--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104506_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104506_W6.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1723</v>
+        <v>6.795</v>
       </c>
       <c r="E2" t="n">
-        <v>8.584899999999999</v>
+        <v>8.972</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4126</v>
+        <v>-2.177</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7723</v>
+        <v>5.7539</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2814</v>
+        <v>6.2649</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5091</v>
+        <v>-0.511</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3588</v>
+        <v>7.3017</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8893</v>
+        <v>7.846</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5865</v>
+        <v>-1.5478</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6079</v>
+        <v>-1.5811</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5171</v>
+        <v>-0.8615</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8347</v>
+        <v>-0.3627</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6823</v>
+        <v>-0.4989</v>
       </c>
       <c r="V2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6516</v>
+        <v>4.2348</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9562</v>
+        <v>3.8796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6954</v>
+        <v>0.3552</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3304</v>
+        <v>2.3391</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5569</v>
+        <v>2.5562</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2265</v>
+        <v>-0.2171</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8143</v>
+        <v>2.795</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5904</v>
+        <v>2.5715</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4839</v>
+        <v>-0.4558</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.548</v>
+        <v>0.1233</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0907</v>
+        <v>0.0439</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4573</v>
+        <v>0.0795</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8769</v>
+        <v>3.8521</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0518</v>
+        <v>2.3327</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8251</v>
+        <v>1.5194</v>
       </c>
       <c r="G4" t="n">
-        <v>1.043</v>
+        <v>1.0596</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9896</v>
+        <v>1.0044</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0533</v>
+        <v>0.0552</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5636</v>
+        <v>1.5456</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9048</v>
+        <v>1.8961</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5206</v>
+        <v>-0.486</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9152</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8466</v>
+        <v>-0.8904</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7652</v>
+        <v>-0.4601</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0814</v>
+        <v>-0.4303</v>
       </c>
       <c r="V4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7794</v>
+        <v>2.0333</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5398</v>
+        <v>2.2841</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7604</v>
+        <v>-0.2508</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9964</v>
+        <v>2.0055</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7151</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2822</v>
+        <v>1.2904</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0584</v>
+        <v>3.0349</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2672</v>
+        <v>1.2476</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.062</v>
+        <v>-1.0295</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.553</v>
+        <v>-0.5325</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4219</v>
+        <v>-0.3379</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4548</v>
+        <v>0.2296</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0329</v>
+        <v>-0.5675</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7097</v>
+        <v>1.9302</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5673</v>
+        <v>1.5468</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1424</v>
+        <v>0.3834</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5904</v>
+        <v>2.5942</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9826</v>
+        <v>1.9818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6078</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3275</v>
+        <v>3.3122</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2902</v>
+        <v>3.275</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7371</v>
+        <v>-0.718</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0395</v>
+        <v>-0.8234</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6261</v>
+        <v>-0.6273</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4134</v>
+        <v>-0.1961</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8871</v>
+        <v>0.7429</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1785</v>
+        <v>0.1713</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7086</v>
+        <v>0.5716</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5296</v>
+        <v>0.5346</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2177</v>
+        <v>0.2264</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3118</v>
+        <v>0.3082</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5263</v>
+        <v>0.5198</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0033</v>
+        <v>0.0148</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0015</v>
+        <v>-0.159</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3463</v>
+        <v>0.1895</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0212</v>
+        <v>0.114</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1669</v>
+        <v>-0.1718</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1881</v>
+        <v>0.2859</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0281</v>
+        <v>0.0269</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8008</v>
+        <v>-0.8013</v>
       </c>
       <c r="I8" t="n">
-        <v>0.829</v>
+        <v>0.8282</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0973</v>
+        <v>-0.1021</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.007</v>
+        <v>0.0871</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0626</v>
+        <v>0.1568</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4934</v>
+        <v>-0.5677</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3505</v>
+        <v>-0.3749</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1429</v>
+        <v>-0.1927</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3062</v>
+        <v>-0.3061</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9033</v>
+        <v>-0.9019</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3522</v>
+        <v>-0.363</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M9" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3744</v>
+        <v>-0.4389</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1601</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.148</v>
+        <v>-0.9477</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3711</v>
+        <v>-2.1586</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2231</v>
+        <v>1.2109</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5857</v>
+        <v>-0.5888</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.87</v>
+        <v>-2.8693</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2843</v>
+        <v>2.2804</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5413</v>
+        <v>-0.5603</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2552</v>
+        <v>-2.2655</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0444</v>
+        <v>-0.0285</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3354</v>
+        <v>-0.1312</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3602</v>
+        <v>0.3289</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1573</v>
+        <v>-1.1213</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0877</v>
+        <v>-1.0516</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.206</v>
+        <v>-0.1754</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2315</v>
+        <v>-2.0951</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4403</v>
+        <v>1.4779</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6718</v>
+        <v>-3.5729</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.434</v>
+        <v>-2.4271</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4157</v>
+        <v>-1.405</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0183</v>
+        <v>-1.022</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1637</v>
+        <v>-1.1816</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5959</v>
+        <v>-0.6</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2702</v>
+        <v>-1.2455</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0924</v>
+        <v>-0.9639</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8347</v>
+        <v>-0.7667</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2577</v>
+        <v>-0.1972</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0115</v>
+        <v>-4.5428</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0297</v>
+        <v>-1.5069</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9819</v>
+        <v>-3.0359</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9625</v>
+        <v>-0.9422</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3682</v>
+        <v>-0.354</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5944</v>
+        <v>-0.5881</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9126</v>
+        <v>0.9046</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4676</v>
+        <v>0.4654</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8752</v>
+        <v>-1.8467</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7976</v>
+        <v>-0.3518</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8347</v>
+        <v>-0.2929</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0372</v>
+        <v>-0.0589</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.571</v>
+        <v>-2.5659</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.0565</v>
+        <v>10.4277</v>
       </c>
       <c r="E14" t="n">
-        <v>16.331</v>
+        <v>16.38249999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.2746</v>
+        <v>-5.954499999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>10.1432</v>
+        <v>10.1931</v>
       </c>
       <c r="H14" t="n">
-        <v>6.211199999999999</v>
+        <v>6.244900000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>3.931699999999999</v>
+        <v>3.9483</v>
       </c>
       <c r="J14" t="n">
-        <v>17.407</v>
+        <v>17.2068</v>
       </c>
       <c r="K14" t="n">
-        <v>13.7823</v>
+        <v>13.6497</v>
       </c>
       <c r="L14" t="n">
-        <v>3.6245</v>
+        <v>3.557100000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.263700000000002</v>
+        <v>-7.013700000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.571</v>
+        <v>-7.404699999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3072999999999999</v>
+        <v>0.3910000000000002</v>
       </c>
       <c r="P14" t="n">
-        <v>2.268400000000001</v>
+        <v>2.2764</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3418</v>
+        <v>-11.3818</v>
       </c>
       <c r="R14" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.2476</v>
+        <v>-4.923</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.8107</v>
+        <v>-3.463000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4367</v>
+        <v>-1.46</v>
       </c>
       <c r="V14" t="n">
-        <v>2.892400000000001</v>
+        <v>2.8816</v>
       </c>
       <c r="W14" t="n">
-        <v>14.0762</v>
+        <v>14.0203</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.184</v>
+        <v>-11.1387</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.555</v>
+        <v>3.5809</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4103</v>
+        <v>4.3121</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8554</v>
+        <v>-0.7312</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6632</v>
+        <v>1.6472</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4877</v>
+        <v>-0.4882</v>
       </c>
       <c r="I15" t="n">
-        <v>2.151</v>
+        <v>2.1354</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4257</v>
+        <v>4.3891</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1575</v>
+        <v>2.1406</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2682</v>
+        <v>2.2484</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7624</v>
+        <v>-2.7419</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6452</v>
+        <v>-2.6288</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0402</v>
+        <v>1.002</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5202</v>
+        <v>0.427</v>
       </c>
       <c r="U15" t="n">
-        <v>0.48</v>
+        <v>0.575</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4113</v>
+        <v>3.4556</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1339</v>
+        <v>6.6656</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.7226</v>
+        <v>-3.2099</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0607</v>
+        <v>3.0512</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7676</v>
+        <v>2.7686</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2931</v>
+        <v>0.2826</v>
       </c>
       <c r="J16" t="n">
-        <v>5.0981</v>
+        <v>5.0571</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1387</v>
+        <v>4.1196</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9594</v>
+        <v>0.9375</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0374</v>
+        <v>-2.0059</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3711</v>
+        <v>-1.351</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2204</v>
+        <v>-0.1615</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9739</v>
+        <v>-0.3836</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2465</v>
+        <v>0.2221</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5692</v>
+        <v>2.4769</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8368</v>
+        <v>1.5302</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.9467</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8422</v>
+        <v>-1.8319</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1545</v>
+        <v>-1.1437</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6877</v>
+        <v>-0.6882</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.532</v>
+        <v>-0.5415</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.492</v>
+        <v>-0.4966</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.04</v>
+        <v>-0.0449</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3103</v>
+        <v>-1.2904</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3617</v>
+        <v>0.5364</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5898</v>
+        <v>0.1204</v>
       </c>
       <c r="U17" t="n">
-        <v>0.228</v>
+        <v>0.416</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5286</v>
+        <v>-0.2785</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8782</v>
+        <v>2.4515</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3496</v>
+        <v>-2.7299</v>
       </c>
       <c r="G18" t="n">
         <v>0.4289</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1357</v>
+        <v>0.1323</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2932</v>
+        <v>0.2966</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9134</v>
+        <v>0.9023</v>
       </c>
       <c r="K18" t="n">
-        <v>0.876</v>
+        <v>0.8651</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4844</v>
+        <v>-0.4734</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2189</v>
+        <v>1.4017</v>
       </c>
       <c r="T18" t="n">
-        <v>2.099</v>
+        <v>0.6873</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1199</v>
+        <v>0.7145</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GARCIA</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7284</v>
+        <v>-0.6993</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2087</v>
+        <v>0.5793</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5198</v>
+        <v>-1.2786</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5913</v>
+        <v>-0.5564</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1573</v>
+        <v>-0.4999</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7486</v>
+        <v>-0.0565</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7864</v>
+        <v>0.8791</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.8791</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7864</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.805</v>
+        <v>-1.4355</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>-1.3789</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.0565</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8629</v>
+        <v>-0.1429</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5777</v>
+        <v>-0.2998</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2852</v>
+        <v>0.1568</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9012</v>
+        <v>-1.0317</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4528</v>
+        <v>0.0432</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.354</v>
+        <v>-1.075</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6754</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2001</v>
+        <v>-2.2245</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5247</v>
+        <v>1.5254</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7066</v>
+        <v>0.665</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2242</v>
+        <v>0.1886</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3821</v>
+        <v>-1.3642</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4243</v>
+        <v>-2.4132</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9745</v>
+        <v>0.8754</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1221</v>
+        <v>0.7731</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1476</v>
+        <v>0.1024</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9156</v>
+        <v>-1.0353</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4658</v>
+        <v>0.6006</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3814</v>
+        <v>-1.6359</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5608</v>
+        <v>-0.0955</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5022</v>
+        <v>2.6484</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0586</v>
+        <v>-2.7439</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8832</v>
+        <v>1.7949</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8832</v>
+        <v>2.7784</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.9835</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.444</v>
+        <v>-1.8904</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3853</v>
+        <v>-0.13</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0586</v>
+        <v>-1.7604</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3548</v>
+        <v>0.2682</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4174</v>
+        <v>-0.1652</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0626</v>
+        <v>0.4335</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>S. GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9344</v>
+        <v>-1.2925</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7592</v>
+        <v>-0.6829</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6937</v>
+        <v>-0.6096</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0877</v>
+        <v>-1.5909</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6551</v>
+        <v>0.1579</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7428</v>
+        <v>-1.7488</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8226</v>
+        <v>-0.7896</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7982</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9756</v>
+        <v>-0.7896</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9103</v>
+        <v>-0.8012</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1431</v>
+        <v>0.1579</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7672</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3536</v>
+        <v>0.2984</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0484</v>
+        <v>0.1067</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4019</v>
+        <v>0.1917</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0128</v>
+        <v>-1.4385</v>
       </c>
       <c r="E23" t="n">
-        <v>0.51</v>
+        <v>0.3793</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5228</v>
+        <v>-1.8179</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8274</v>
+        <v>-0.8275</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3103</v>
+        <v>-0.3075</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5171</v>
+        <v>-0.52</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5765</v>
+        <v>0.5631</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4039</v>
+        <v>-1.3906</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2281</v>
+        <v>-1.221</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9073</v>
+        <v>0.4784</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3871</v>
+        <v>0.2715</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5202</v>
+        <v>0.2069</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9625</v>
+        <v>-4.0065</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.809</v>
+        <v>-2.0721</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1534</v>
+        <v>-1.9345</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1519</v>
+        <v>-3.1563</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.2825</v>
+        <v>-3.2937</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1307</v>
+        <v>0.1373</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5589</v>
+        <v>-1.579</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.7081</v>
+        <v>-1.7279</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.593</v>
+        <v>-1.5774</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5744</v>
+        <v>-1.5658</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0109</v>
+        <v>-0.0582</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1089</v>
+        <v>-0.1258</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1198</v>
+        <v>0.0675</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.5748</v>
+        <v>-1.5628</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6692</v>
+        <v>-4.8605</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1136</v>
+        <v>-5.0308</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4445</v>
+        <v>0.1703</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.8351</v>
+        <v>-3.8347</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.1904</v>
+        <v>-2.1886</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.6446</v>
+        <v>-1.6461</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.5867</v>
+        <v>-2.6156</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4889</v>
+        <v>-0.5073</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.0979</v>
+        <v>-2.1083</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.2484</v>
+        <v>-1.2191</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.7016</v>
+        <v>-1.6813</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>0.871</v>
+        <v>0.6783</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0998</v>
+        <v>0.0205</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9708</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.9965</v>
+        <v>-4.9499</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.0412</v>
+        <v>-2.8215</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9553</v>
+        <v>-2.1284</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.7242</v>
+        <v>-2.7281</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.7993</v>
+        <v>-1.8062</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.6984</v>
+        <v>-1.7112</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.7357</v>
+        <v>-1.7484</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.0258</v>
+        <v>-1.0169</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0472</v>
+        <v>0.0953</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2559</v>
+        <v>0.0675</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.0565</v>
+        <v>-10.0793</v>
       </c>
       <c r="E27" t="n">
-        <v>6.274500000000003</v>
+        <v>5.954500000000003</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.3311</v>
+        <v>-16.0339</v>
       </c>
       <c r="G27" t="n">
-        <v>-10.1432</v>
+        <v>-10.1931</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.2113</v>
+        <v>-6.245099999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.9316</v>
+        <v>-3.9481</v>
       </c>
       <c r="J27" t="n">
-        <v>7.263699999999998</v>
+        <v>7.0137</v>
       </c>
       <c r="K27" t="n">
-        <v>7.570900000000002</v>
+        <v>7.4048</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.3072999999999998</v>
+        <v>-0.3911999999999994</v>
       </c>
       <c r="M27" t="n">
-        <v>-17.407</v>
+        <v>-17.2069</v>
       </c>
       <c r="N27" t="n">
-        <v>-13.7824</v>
+        <v>-13.6498</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.624500000000001</v>
+        <v>-3.5571</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q27" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R27" t="n">
-        <v>11.3418</v>
+        <v>11.3818</v>
       </c>
       <c r="S27" t="n">
-        <v>5.247400000000001</v>
+        <v>5.2715</v>
       </c>
       <c r="T27" t="n">
-        <v>1.436600000000001</v>
+        <v>1.4599</v>
       </c>
       <c r="U27" t="n">
-        <v>3.8106</v>
+        <v>3.8117</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.8925</v>
+        <v>-2.8814</v>
       </c>
       <c r="W27" t="n">
-        <v>11.1839</v>
+        <v>11.1388</v>
       </c>
       <c r="X27" t="n">
-        <v>-14.0764</v>
+        <v>-14.0204</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104506_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104506_W6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.1387</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104506_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-14.0204</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
